--- a/technology_surveys/011_smart_lock_security_perception_survey--technology_surveys.xlsx
+++ b/technology_surveys/011_smart_lock_security_perception_survey--technology_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -999,8 +999,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'security'}</t>
+          <t>security</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Security'}</t>
+          <t>Security</t>
         </is>
       </c>
     </row>
@@ -1045,12 +1045,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'cost'}</t>
+          <t>cost</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Cost'}</t>
+          <t>Cost</t>
         </is>
       </c>
     </row>
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'aesthetics'}</t>
+          <t>aesthetics</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Aesthetics'}</t>
+          <t>Aesthetics</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Very Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -1096,12 +1096,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -1113,12 +1113,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1130,12 +1130,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Dissatisfied'}</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1147,12 +1147,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Very Dissatisfied'}</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'private'}</t>
+          <t>private</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Private'}</t>
+          <t>Private</t>
         </is>
       </c>
     </row>
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'public'}</t>
+          <t>public</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Public'}</t>
+          <t>Public</t>
         </is>
       </c>
     </row>
@@ -1198,12 +1198,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'1-10'}</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': '1-10'}</t>
+          <t>1-10</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'11-50'}</t>
+          <t>11-50</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': '11-50'}</t>
+          <t>11-50</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'51-200'}</t>
+          <t>51-200</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': '51-200'}</t>
+          <t>51-200</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'201-1000'}</t>
+          <t>201-1000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': '201-1000'}</t>
+          <t>201-1000</t>
         </is>
       </c>
     </row>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'1001-5000'}</t>
+          <t>1001-5000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': '1001-5000'}</t>
+          <t>1001-5000</t>
         </is>
       </c>
     </row>
@@ -1283,12 +1283,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'5001-10000'}</t>
+          <t>5001-10000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': '5001-10000'}</t>
+          <t>5001-10000</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_10001}</t>
+          <t>10001</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 10001}</t>
+          <t>10001</t>
         </is>
       </c>
     </row>
@@ -1317,12 +1317,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'10000+'}</t>
+          <t>10000+</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': '10000+'}</t>
+          <t>10000+</t>
         </is>
       </c>
     </row>
